--- a/outputs/56953.xlsx
+++ b/outputs/56953.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="6">
   <si>
     <t xml:space="preserve">EG740F</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t xml:space="preserve">(Nm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engine</t>
   </si>
   <si>
     <t xml:space="preserve">Engine HS</t>
@@ -219,79 +216,79 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -562,7 +559,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -586,7 +583,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>3</v>
@@ -595,7 +592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>70</v>
       </c>
@@ -619,23 +616,21 @@
         <v/>
       </c>
       <c r="I3" s="7" t="n">
-        <f aca="false" t="array" ref="I3:I3">IF(ROW(A1)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($A$2:$A$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A1)),1))</f>
         <v>70</v>
       </c>
       <c r="J3" s="7" t="n">
-        <f aca="false" t="array" ref="J3:J3">IF(ROW(A1)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($B$2:$B$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A1)),1))</f>
         <v>900</v>
       </c>
       <c r="K3" s="7" t="n">
-        <f aca="false" t="array" ref="K3:K3">IF(ROW(A1)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($C$2:$C$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A1)),1))</f>
+        <f aca="false">B3*1.65</f>
         <v>1485</v>
       </c>
       <c r="L3" s="7" t="n">
-        <f aca="false" t="array" ref="L3:L3">IF(ROW(A1)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($D$2:$D$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A1)),1))</f>
+        <f aca="false">A3*9550/C3</f>
         <v>450.16835016835</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>70</v>
       </c>
@@ -660,23 +655,22 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <f aca="false" t="array" ref="I4:I4">IF(ROW(A2)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($A$2:$A$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A2)),1))</f>
         <v>70</v>
       </c>
       <c r="J4" s="7" t="n">
-        <f aca="false" t="array" ref="J4:J4">IF(ROW(A2)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($B$2:$B$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A2)),1))</f>
+        <f aca="false">B3+100</f>
         <v>1000</v>
       </c>
       <c r="K4" s="7" t="n">
-        <f aca="false" t="array" ref="K4:K4">IF(ROW(A2)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($C$2:$C$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A2)),1))</f>
+        <f aca="false">B4*1.65</f>
         <v>1650</v>
       </c>
       <c r="L4" s="7" t="n">
-        <f aca="false" t="array" ref="L4:L4">IF(ROW(A2)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($D$2:$D$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A2)),1))</f>
+        <f aca="false">A4*9550/C4</f>
         <v>405.151515151515</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>70</v>
       </c>
@@ -697,23 +691,22 @@
         <v/>
       </c>
       <c r="I5" s="7" t="n">
-        <f aca="false" t="array" ref="I5:I5">IF(ROW(A3)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($A$2:$A$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A3)),1))</f>
         <v>70</v>
       </c>
       <c r="J5" s="7" t="n">
-        <f aca="false" t="array" ref="J5:J5">IF(ROW(A3)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($B$2:$B$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A3)),1))</f>
+        <f aca="false">B4+100</f>
         <v>1100</v>
       </c>
       <c r="K5" s="7" t="n">
-        <f aca="false" t="array" ref="K5:K5">IF(ROW(A3)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($C$2:$C$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A3)),1))</f>
+        <f aca="false">B5*1.65</f>
         <v>1815</v>
       </c>
       <c r="L5" s="7" t="n">
-        <f aca="false" t="array" ref="L5:L5">IF(ROW(A3)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($D$2:$D$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A3)),1))</f>
+        <f aca="false">A5*9550/C5</f>
         <v>368.31955922865</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
         <v>70</v>
       </c>
@@ -734,28 +727,27 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <f aca="false" t="array" ref="I6:I6">IF(ROW(A4)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($A$2:$A$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A4)),1))</f>
         <v>70</v>
       </c>
       <c r="J6" s="7" t="n">
-        <f aca="false" t="array" ref="J6:J6">IF(ROW(A4)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($B$2:$B$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A4)),1))</f>
+        <f aca="false">B5+100</f>
         <v>1200</v>
       </c>
       <c r="K6" s="7" t="n">
-        <f aca="false" t="array" ref="K6:K6">IF(ROW(A4)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($C$2:$C$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A4)),1))</f>
+        <f aca="false">B6*1.65</f>
         <v>1980</v>
       </c>
       <c r="L6" s="7" t="n">
-        <f aca="false" t="array" ref="L6:L6">IF(ROW(A4)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($D$2:$D$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A4)),1))</f>
+        <f aca="false">A6*9550/C6</f>
         <v>337.626262626263</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>3</v>
@@ -763,24 +755,20 @@
       <c r="D7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="7" t="n">
-        <f aca="false" t="array" ref="I7:I7">IF(ROW(A5)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($A$2:$A$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A5)),1))</f>
-        <v>70</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <f aca="false" t="array" ref="J7:J7">IF(ROW(A5)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($B$2:$B$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A5)),1))</f>
-        <v>700</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <f aca="false" t="array" ref="K7:K7">IF(ROW(A5)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($C$2:$C$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A5)),1))</f>
-        <v>1428</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <f aca="false" t="array" ref="L7:L7">IF(ROW(A5)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($D$2:$D$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A5)),1))</f>
-        <v>468.137254901961</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>70</v>
       </c>
@@ -796,20 +784,18 @@
         <v>468.137254901961</v>
       </c>
       <c r="I8" s="7" t="n">
-        <f aca="false" t="array" ref="I8:I8">IF(ROW(A6)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($A$2:$A$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A6)),1))</f>
         <v>70</v>
       </c>
       <c r="J8" s="7" t="n">
-        <f aca="false" t="array" ref="J8:J8">IF(ROW(A6)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($B$2:$B$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A6)),1))</f>
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K8" s="7" t="n">
-        <f aca="false" t="array" ref="K8:K8">IF(ROW(A6)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($C$2:$C$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A6)),1))</f>
-        <v>1632</v>
+        <f aca="false">B8*2.04</f>
+        <v>1428</v>
       </c>
       <c r="L8" s="7" t="n">
-        <f aca="false" t="array" ref="L8:L8">IF(ROW(A6)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($D$2:$D$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A6)),1))</f>
-        <v>409.620098039216</v>
+        <f aca="false">A8*9550/C8</f>
+        <v>468.137254901961</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -828,24 +814,23 @@
         <f aca="false">A9*9550/C9</f>
         <v>409.620098039216</v>
       </c>
-      <c r="I9" s="7" t="str">
-        <f aca="false" t="array" ref="I9:I9">IF(ROW(A7)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($A$2:$A$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A7)),1))</f>
-        <v/>
-      </c>
-      <c r="J9" s="7" t="str">
-        <f aca="false" t="array" ref="J9:J9">IF(ROW(A7)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($B$2:$B$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A7)),1))</f>
-        <v/>
-      </c>
-      <c r="K9" s="7" t="str">
-        <f aca="false" t="array" ref="K9:K9">IF(ROW(A7)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($C$2:$C$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A7)),1))</f>
-        <v/>
-      </c>
-      <c r="L9" s="7" t="str">
-        <f aca="false" t="array" ref="L9:L9">IF(ROW(A7)&gt;COUNTIF($A$2:$A$15,$F$2),"",INDEX($D$2:$D$15,_xlfn.AGGREGATE(15,6,IF($A$2:$A$15=$F$2,ROW($A$2:$A$15)-ROW($A$2)+1,""),ROW(A7)),1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I9" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <f aca="false">B8+100</f>
+        <v>800</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <f aca="false">B9*2.04</f>
+        <v>1632</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <f aca="false">A9*9550/C9</f>
+        <v>409.620098039216</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
         <v>1</v>
       </c>
@@ -863,7 +848,7 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="n">
         <v>100</v>
       </c>
@@ -883,7 +868,7 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="n">
         <v>100</v>
       </c>
@@ -904,7 +889,7 @@
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="n">
         <v>100</v>
       </c>
@@ -925,12 +910,12 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>3</v>
@@ -939,7 +924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="n">
         <v>100</v>
       </c>
